--- a/human_resources_surveys/044_post_interview_questionnaire--human_resources_surveys.xlsx
+++ b/human_resources_surveys/044_post_interview_questionnaire--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1142,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data_management</t>
+          <t>data_strategy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Data Management</t>
+          <t>Data Strategy</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>data_strategy</t>
+          <t>big_data_engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Data Strategy</t>
+          <t>Big Data Engineering</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>business_intelligence</t>
+          <t>machine_learning_engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>Machine Learning Engineering</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data_science</t>
+          <t>data_analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Data Analytics</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data_engineering</t>
+          <t>business_analytics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Business Analytics</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>big_data_engineering</t>
+          <t>project_development</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Big Data Engineering</t>
+          <t>Project Development</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>machine_learning_engineering</t>
+          <t>team_management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineering</t>
+          <t>Team Management</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>data_analytics</t>
+          <t>team_development</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Data Analytics</t>
+          <t>Team Development</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>business_analytics</t>
+          <t>data_development</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Business Analytics</t>
+          <t>Data Development</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>business_intelligence</t>
+          <t>financial_development</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>Financial Development</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>business_development</t>
+          <t>financial_engineering</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Financial Engineering</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>big_data_development</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Big Data Development</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>project_development</t>
+          <t>big_data_management</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Project Development</t>
+          <t>Big Data Management</t>
         </is>
       </c>
     </row>
@@ -2263,452 +2263,180 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>team_management</t>
+          <t>business_engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Team Management</t>
+          <t>Business Engineering</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>team_development</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Team Development</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data_development</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Data Development</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data_management</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Data Management</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>financial_development</t>
+          <t>miami</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Financial Development</t>
+          <t>Miami</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>financial_engineering</t>
+          <t>san_francisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Financial Engineering</t>
+          <t>San Francisco</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data_engineering</t>
+          <t>austin</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Austin</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>big_data_engineering</t>
+          <t>boston</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Big Data Engineering</t>
+          <t>Boston</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>big_data_development</t>
+          <t>washington_dc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Big Data Development</t>
+          <t>Washington DC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>big_data_management</t>
+          <t>dallas</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Big Data Management</t>
+          <t>Dallas</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>business_development</t>
+          <t>houston</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
-        <is>
-          <t>Business Development</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>business_engineering</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Business Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>business_management</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Business Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>business_strategy</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Business Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>business_development</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Business Development</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>business_management</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Business Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>business_strategy</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Business Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>new_york</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>los_angeles</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>chicago</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>miami</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>san_francisco</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>austin</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>boston</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>washington_dc</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Washington DC</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>dallas</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>houston</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
